--- a/Outputs/PtX_demand_IE.xlsx
+++ b/Outputs/PtX_demand_IE.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,32 +488,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>2030</v>
       </c>
       <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="n">
-        <v>0.0003866335395407821</v>
-      </c>
+      <c r="D2" t="n">
+        <v>0.002827009255588008</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.001063006228755645</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="n">
-        <v>1.258167754132802e-09</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0.0002302426784932863</v>
-      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -522,17 +520,23 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>0.0003866335395407821</v>
+      </c>
       <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>1.258167754132802e-09</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.0002302426784932863</v>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ammonia</t>
+          <t>Methanol</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -551,7 +555,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Synthetic Gases</t>
+          <t>Ammonia</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -570,7 +574,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Biogenic Gases</t>
+          <t>Synthetic Gases</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -578,24 +582,18 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="n">
-        <v>0.0001276004121486529</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.000129677720281579</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="n">
-        <v>3.452513043873888e-05</v>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Fossil Gases</t>
+          <t>Biogenic Gases</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -603,14 +601,16 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>0.0001276004121486529</v>
+      </c>
       <c r="F7" t="n">
-        <v>0.0014890748389714</v>
+        <v>0.000129677720281579</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="n">
-        <v>0.0001599571264707139</v>
+        <v>3.452513043873888e-05</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -618,7 +618,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Synthetic Liquids</t>
+          <t>Fossil Gases</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -627,17 +627,21 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>0.0014890748389714</v>
+      </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="n">
+        <v>0.0001599571264707139</v>
+      </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Biogenic Liquids</t>
+          <t>Synthetic Liquids</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -646,29 +650,17 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="n">
-        <v>0.007128437630251732</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1.791069058325931e-05</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.003425970247539691</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0.007656994072575</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.522257158030819e-06</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.003341062137162474</v>
-      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Fossil Liquids</t>
+          <t>Biogenic Liquids</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -678,28 +670,28 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
-        <v>0.0689140591071683</v>
+        <v>0.007128437630251732</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0001261397415553</v>
+        <v>1.791069058325931e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>0.03130859249984613</v>
+        <v>0.003425970247539691</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0477467910813372</v>
+        <v>0.007656994072575</v>
       </c>
       <c r="J10" t="n">
-        <v>9.214225780114264e-06</v>
+        <v>1.522257158030819e-06</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0326787456338598</v>
+        <v>0.003341062137162474</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Liquids</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -707,20 +699,30 @@
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
-      <c r="E11" t="n">
-        <v>0.001701972684689266</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>0.0689140591071683</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0001261397415553</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.03130859249984613</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.0477467910813372</v>
+      </c>
+      <c r="J11" t="n">
+        <v>9.214225780114264e-06</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0326787456338598</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Renewable Energy Carrier</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -729,7 +731,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>0.001242591300436453</v>
+        <v>0.001701972684689266</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -741,7 +743,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Overall Demand</t>
+          <t>Fossil Rest</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -750,83 +752,87 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>0.003072164397274372</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.07804788283621379</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.0001440504321385593</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.03473456400555358</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0.05582851008931494</v>
-      </c>
-      <c r="J13" t="n">
-        <v>1.073648293814508e-05</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.03601980777102227</v>
-      </c>
+        <v>0.01233172541326595</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Renewable Energy Carrier</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2040</v>
+        <v>2030</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="n">
-        <v>0.0018505625988016</v>
-      </c>
+      <c r="E14" t="n">
+        <v>0.001242591300436453</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="n">
-        <v>1.053225375815418e-07</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0.0003234085448113575</v>
-      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>Overall Demand</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2040</v>
+        <v>2030</v>
       </c>
       <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="D15" t="n">
+        <v>0.002827009255588008</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.01646689603929597</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.07804788283621379</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.0001440504321385593</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.03473456400555358</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.05582851008931494</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.073648293814508e-05</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.03601980777102227</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ammonia</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>2040</v>
       </c>
       <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+      <c r="D16" t="n">
+        <v>0.002518016004647162</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.00116810709905385</v>
+      </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -837,7 +843,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Synthetic Gases</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -847,12 +853,14 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
-        <v>6.895466904779869e-10</v>
+        <v>0.0018505625988016</v>
       </c>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>1.053225375815418e-07</v>
+      </c>
       <c r="I17" t="n">
-        <v>9.568241845163511e-11</v>
+        <v>0.0003234085448113575</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -860,7 +868,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Biogenic Gases</t>
+          <t>Methanol</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -868,24 +876,18 @@
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="n">
-        <v>0.0005179764388878285</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.0001565225644405462</v>
-      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="n">
-        <v>6.574642626760885e-05</v>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Fossil Gases</t>
+          <t>Ammonia</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -894,21 +896,17 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="n">
-        <v>0.0008164658281451999</v>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="n">
-        <v>0.0001681108248057366</v>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Synthetic Liquids</t>
+          <t>Synthetic Gases</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -917,17 +915,21 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="n">
+        <v>6.895466904779869e-10</v>
+      </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="n">
+        <v>9.568241845163511e-11</v>
+      </c>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Biogenic Liquids</t>
+          <t>Biogenic Gases</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -935,30 +937,24 @@
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="n">
+        <v>0.0005179764388878285</v>
+      </c>
       <c r="F21" t="n">
-        <v>0.003167898218339361</v>
-      </c>
-      <c r="G21" t="n">
-        <v>2.919738046383545e-05</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.004171596541923978</v>
-      </c>
+        <v>0.0001565225644405462</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="n">
-        <v>0.0049793053757623</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1.849295387162815e-06</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.003783400348455214</v>
-      </c>
+        <v>6.574642626760885e-05</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Fossil Liquids</t>
+          <t>Fossil Gases</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -968,28 +964,20 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="n">
-        <v>0.0189383147124399</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.0001356072351823</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.02951858216655263</v>
-      </c>
+        <v>0.0008164658281451999</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="n">
-        <v>0.0209796775230359</v>
-      </c>
-      <c r="J22" t="n">
-        <v>8.176801028651042e-06</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0.0316918999651766</v>
-      </c>
+        <v>0.0001681108248057366</v>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Synthetic Liquids</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -997,9 +985,7 @@
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
-      <c r="E23" t="n">
-        <v>0.001623178834603923</v>
-      </c>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
@@ -1010,7 +996,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Renewable Energy Carrier</t>
+          <t>Biogenic Liquids</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1018,20 +1004,30 @@
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="n">
-        <v>0.005192561614440269</v>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="n">
+        <v>0.003167898218339361</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2.919738046383545e-05</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.004171596541923978</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.0049793053757623</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.849295387162815e-06</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.003783400348455214</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Overall Demand</t>
+          <t>Fossil Liquids</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1039,65 +1035,61 @@
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="n">
-        <v>0.00733371688793202</v>
-      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="n">
-        <v>0.0249297646117133</v>
+        <v>0.0189383147124399</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0001648046156461354</v>
+        <v>0.0001356072351823</v>
       </c>
       <c r="H25" t="n">
-        <v>0.03369028403101419</v>
+        <v>0.02951858216655263</v>
       </c>
       <c r="I25" t="n">
-        <v>0.02651624879036532</v>
+        <v>0.0209796775230359</v>
       </c>
       <c r="J25" t="n">
-        <v>1.002609641581386e-05</v>
+        <v>8.176801028651042e-06</v>
       </c>
       <c r="K25" t="n">
-        <v>0.03547530031363182</v>
+        <v>0.0316918999651766</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Hydrogen</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="n">
-        <v>0.0025703545990333</v>
-      </c>
+      <c r="E26" t="n">
+        <v>0.001623178834603923</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="n">
-        <v>1.785132176394185e-07</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.0005129114715790451</v>
-      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Methanol</t>
+          <t>Fossil Rest</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="n">
+        <v>0.008565807079992141</v>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
@@ -1108,15 +1100,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Ammonia</t>
+          <t>Renewable Energy Carrier</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="n">
+        <v>0.005192561614440269</v>
+      </c>
       <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
@@ -1127,55 +1121,65 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Synthetic Gases</t>
+          <t>Overall Demand</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2050</v>
+        <v>2040</v>
       </c>
       <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+      <c r="D29" t="n">
+        <v>0.002518016004647162</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.01706763106697801</v>
+      </c>
       <c r="F29" t="n">
-        <v>7.475041808045828e-09</v>
-      </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+        <v>0.0249297646117133</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.0001648046156461354</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.03369028403101419</v>
+      </c>
       <c r="I29" t="n">
-        <v>2.015152566902412e-09</v>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
+        <v>0.02651624879036532</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.002609641581386e-05</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.03547530031363182</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Biogenic Gases</t>
+          <t>Power</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>2050</v>
       </c>
       <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="n">
+        <v>0.002172357481914139</v>
+      </c>
       <c r="E30" t="n">
-        <v>0.001322684415299623</v>
-      </c>
-      <c r="F30" t="n">
-        <v>2.818187897676415e-05</v>
-      </c>
+        <v>0.001285679283736252</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="n">
-        <v>1.934670915493983e-05</v>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Fossil Gases</t>
+          <t>Hydrogen</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -1185,12 +1189,14 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
-        <v>5.648282864018704e-05</v>
+        <v>0.0025703545990333</v>
       </c>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="H31" t="n">
+        <v>1.785132176394185e-07</v>
+      </c>
       <c r="I31" t="n">
-        <v>6.513257528425315e-05</v>
+        <v>0.0005129114715790451</v>
       </c>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
@@ -1198,7 +1204,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Synthetic Liquids</t>
+          <t>Methanol</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1207,29 +1213,17 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="n">
-        <v>1.249330813810234e-11</v>
-      </c>
-      <c r="G32" t="n">
-        <v>1.075181711816921e-12</v>
-      </c>
-      <c r="H32" t="n">
-        <v>1.606411534532855e-10</v>
-      </c>
-      <c r="I32" t="n">
-        <v>8.567529130007003e-11</v>
-      </c>
-      <c r="J32" t="n">
-        <v>1.266550178375058e-14</v>
-      </c>
-      <c r="K32" t="n">
-        <v>2.612182969878195e-10</v>
-      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Biogenic Liquids</t>
+          <t>Ammonia</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1238,29 +1232,17 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="n">
-        <v>0.0003073122161435503</v>
-      </c>
-      <c r="G33" t="n">
-        <v>5.217059266314125e-05</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.005465103009091464</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.0012772935523164</v>
-      </c>
-      <c r="J33" t="n">
-        <v>2.378486713250105e-06</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0.005388433374178804</v>
-      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Fossil Liquids</t>
+          <t>Synthetic Gases</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1270,28 +1252,20 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
       <c r="F34" t="n">
-        <v>0.0008654151399991</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0.0001223119831201</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.02676532891359928</v>
-      </c>
+        <v>7.475041808045828e-09</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="n">
-        <v>0.0037821014012264</v>
-      </c>
-      <c r="J34" t="n">
-        <v>7.038188824556429e-06</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0.02953301039053015</v>
-      </c>
+        <v>2.015152566902412e-09</v>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Biogenic Gases</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1300,19 +1274,23 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="n">
-        <v>0.001521101885649291</v>
-      </c>
-      <c r="F35" t="inlineStr"/>
+        <v>0.001322684415299623</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.818187897676415e-05</v>
+      </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
+      <c r="I35" t="n">
+        <v>1.934670915493983e-05</v>
+      </c>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Renewable Energy Carrier</t>
+          <t>Fossil Gases</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1320,20 +1298,22 @@
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="n">
-        <v>0.01361484606639825</v>
-      </c>
-      <c r="F36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="n">
+        <v>5.648282864018704e-05</v>
+      </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="n">
+        <v>6.513257528425315e-05</v>
+      </c>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Overall Demand</t>
+          <t>Synthetic Liquids</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1341,25 +1321,181 @@
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="n">
-        <v>0.01645863236734716</v>
-      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="n">
+        <v>1.249330813810234e-11</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1.075181711816921e-12</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.606411534532855e-10</v>
+      </c>
+      <c r="I37" t="n">
+        <v>8.567529130007003e-11</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.266550178375058e-14</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.612182969878195e-10</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Biogenic Liquids</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="n">
+        <v>0.0003073122161435503</v>
+      </c>
+      <c r="G38" t="n">
+        <v>5.217059266314125e-05</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.005465103009091464</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.0012772935523164</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.378486713250105e-06</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.005388433374178804</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Fossil Liquids</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="n">
+        <v>0.0008654151399991</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.0001223119831201</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.02676532891359928</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.0037821014012264</v>
+      </c>
+      <c r="J39" t="n">
+        <v>7.038188824556429e-06</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.02953301039053015</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Biomass [Solid]</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="n">
+        <v>0.001521101885649291</v>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Fossil Rest</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Renewable Energy Carrier</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="n">
+        <v>0.01361484606639825</v>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Overall Demand</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2050</v>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="n">
+        <v>0.002172357481914139</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.01774431165108341</v>
+      </c>
+      <c r="F43" t="n">
         <v>0.003827754150328017</v>
       </c>
-      <c r="G37" t="n">
+      <c r="G43" t="n">
         <v>0.000174482576858423</v>
       </c>
-      <c r="H37" t="n">
+      <c r="H43" t="n">
         <v>0.03223061059654954</v>
       </c>
-      <c r="I37" t="n">
+      <c r="I43" t="n">
         <v>0.005656787810388897</v>
       </c>
-      <c r="J37" t="n">
+      <c r="J43" t="n">
         <v>9.416675550472036e-06</v>
       </c>
-      <c r="K37" t="n">
+      <c r="K43" t="n">
         <v>0.03492144402592725</v>
       </c>
     </row>

--- a/Outputs/PtX_demand_IE.xlsx
+++ b/Outputs/PtX_demand_IE.xlsx
@@ -501,11 +501,19 @@
       <c r="E2" t="n">
         <v>0.001063006228755645</v>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>0.008348367252065949</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0007252559397565</v>
+      </c>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="I2" t="n">
+        <v>0.0034352186015682</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.379491834718436e-05</v>
+      </c>
       <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -722,7 +730,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Residuals</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -731,7 +739,7 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="n">
-        <v>0.001701972684689266</v>
+        <v>0.01233172541326595</v>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
@@ -743,7 +751,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Fossil Rest</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -752,7 +760,7 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="n">
-        <v>0.01233172541326595</v>
+        <v>0.001701972684689266</v>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
@@ -799,19 +807,19 @@
         <v>0.01646689603929597</v>
       </c>
       <c r="F15" t="n">
-        <v>0.07804788283621379</v>
+        <v>0.08639625008827974</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0001440504321385593</v>
+        <v>0.0008693063718950593</v>
       </c>
       <c r="H15" t="n">
         <v>0.03473456400555358</v>
       </c>
       <c r="I15" t="n">
-        <v>0.05582851008931494</v>
+        <v>0.05926372869088313</v>
       </c>
       <c r="J15" t="n">
-        <v>1.073648293814508e-05</v>
+        <v>2.453140128532944e-05</v>
       </c>
       <c r="K15" t="n">
         <v>0.03601980777102227</v>
@@ -833,11 +841,19 @@
       <c r="E16" t="n">
         <v>0.00116810709905385</v>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>0.02381368402415639</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.0008511547404404</v>
+      </c>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="I16" t="n">
+        <v>0.0112049210072502</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.360499525575504e-05</v>
+      </c>
       <c r="K16" t="inlineStr"/>
     </row>
     <row r="17">
@@ -1058,7 +1074,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Residuals</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1067,7 +1083,7 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="n">
-        <v>0.001623178834603923</v>
+        <v>0.008565807079992141</v>
       </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
@@ -1079,7 +1095,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Fossil Rest</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1088,7 +1104,7 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="n">
-        <v>0.008565807079992141</v>
+        <v>0.001623178834603923</v>
       </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
@@ -1135,19 +1151,19 @@
         <v>0.01706763106697801</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0249297646117133</v>
+        <v>0.04874344863586969</v>
       </c>
       <c r="G29" t="n">
-        <v>0.0001648046156461354</v>
+        <v>0.001015959356086535</v>
       </c>
       <c r="H29" t="n">
         <v>0.03369028403101419</v>
       </c>
       <c r="I29" t="n">
-        <v>0.02651624879036532</v>
+        <v>0.03772116979761553</v>
       </c>
       <c r="J29" t="n">
-        <v>1.002609641581386e-05</v>
+        <v>2.36310916715689e-05</v>
       </c>
       <c r="K29" t="n">
         <v>0.03547530031363182</v>
@@ -1169,11 +1185,19 @@
       <c r="E30" t="n">
         <v>0.001285679283736252</v>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
+      <c r="F30" t="n">
+        <v>0.02782504224018015</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.0009558417989345</v>
+      </c>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="I30" t="n">
+        <v>0.0161815084495004</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.389510900047971e-05</v>
+      </c>
       <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
@@ -1406,7 +1430,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Biomass [Solid]</t>
+          <t>Fossil Residuals</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1414,9 +1438,7 @@
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="n">
-        <v>0.001521101885649291</v>
-      </c>
+      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
@@ -1427,7 +1449,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Fossil Rest</t>
+          <t>Biomass [Solid]</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1435,7 +1457,9 @@
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="n">
+        <v>0.001521101885649291</v>
+      </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
@@ -1481,19 +1505,19 @@
         <v>0.01774431165108341</v>
       </c>
       <c r="F43" t="n">
-        <v>0.003827754150328017</v>
+        <v>0.03165279639050816</v>
       </c>
       <c r="G43" t="n">
-        <v>0.000174482576858423</v>
+        <v>0.001130324375792923</v>
       </c>
       <c r="H43" t="n">
         <v>0.03223061059654954</v>
       </c>
       <c r="I43" t="n">
-        <v>0.005656787810388897</v>
+        <v>0.0218382962598893</v>
       </c>
       <c r="J43" t="n">
-        <v>9.416675550472036e-06</v>
+        <v>2.331178455095175e-05</v>
       </c>
       <c r="K43" t="n">
         <v>0.03492144402592725</v>
